--- a/Bao-cao-KTPM/TestCase-GK.xlsx
+++ b/Bao-cao-KTPM/TestCase-GK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NguyenQuocKhanh\tester\QLDat_Ve\Bao-cao-KTPM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E782DC83-2FA7-4D38-B54C-7A1C87CFACE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6EEA68-994B-47F2-881C-1E342791A715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,30 +319,6 @@
     <t>Kiểm tra trạng thái vé.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Trạng thái: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CONFIRMED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>TC ID: TC06</t>
   </si>
   <si>
@@ -557,6 +533,9 @@
   </si>
   <si>
     <t>Version: v1</t>
+  </si>
+  <si>
+    <t>Trạng thái: CONFIRMED.</t>
   </si>
 </sst>
 </file>
@@ -1343,14 +1322,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1385,7 +1364,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1445,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
@@ -1500,13 +1479,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -1541,14 +1520,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1583,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1643,14 +1622,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1698,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -1739,14 +1718,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1781,7 +1760,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1841,14 +1820,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1896,13 +1875,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -1937,14 +1916,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1979,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2039,14 +2018,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2094,13 +2073,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>125</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>126</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -2135,14 +2114,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2177,7 +2156,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2237,14 +2216,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2292,13 +2271,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>137</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -2333,14 +2312,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2375,7 +2354,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2435,14 +2414,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2490,13 +2469,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
@@ -3418,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>73</v>
@@ -3438,10 +3417,10 @@
         <v>75</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>31</v>
@@ -3476,14 +3455,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3518,7 +3497,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -3578,14 +3557,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3651,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>73</v>
@@ -3671,10 +3650,10 @@
         <v>75</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>31</v>
@@ -3709,14 +3688,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3751,7 +3730,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -3811,14 +3790,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3826,7 +3805,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="12">
@@ -3888,13 +3867,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>31</v>
@@ -3905,13 +3884,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>31</v>
@@ -3946,14 +3925,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3973,7 +3952,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3988,7 +3967,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4048,14 +4027,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -4117,13 +4096,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>31</v>
@@ -4158,14 +4137,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -4200,7 +4179,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4260,14 +4239,14 @@
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -4315,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>31</v>
